--- a/input/mapping/020. OCB_GOLD_TCKH_V_PLA_THUTHUAN_UPL_QUANG.xlsx
+++ b/input/mapping/020. OCB_GOLD_TCKH_V_PLA_THUTHUAN_UPL_QUANG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/MAPPING DONE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{DD7FED2D-C8E1-456A-AAC4-9033A5791684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40DF99F1-14C9-4936-81E4-55D7ABB18470}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{DD7FED2D-C8E1-456A-AAC4-9033A5791684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7065F39-D55A-42D2-8F59-5D48A76071E7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,6 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Script" sheetId="3" r:id="rId2"/>
     <sheet name="V_PLA_THUTHUAN_UPL" sheetId="2" r:id="rId3"/>
-    <sheet name="PLA_THUTHUAN_UPL" sheetId="4" r:id="rId4"/>
-    <sheet name="P_KPI_NAME_DIM_UPL" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
   <si>
     <t>V_PLA_THUTHUAN_UPL  —  Data Lineage Mind Map</t>
   </si>
@@ -281,54 +279,12 @@
   <si>
     <t>B.KPI_LV3</t>
   </si>
-  <si>
-    <t xml:space="preserve">FIELD MAPPING </t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field </t>
-  </si>
-  <si>
-    <t>Data Type</t>
-  </si>
-  <si>
-    <t>Transform Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform Logic </t>
-  </si>
-  <si>
-    <t>nvarchar(255)</t>
-  </si>
-  <si>
-    <t>datetime</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>decimal(24,6)</t>
-  </si>
-  <si>
-    <t>decimal(20,2)</t>
-  </si>
-  <si>
-    <t>decimal(8,0)</t>
-  </si>
-  <si>
-    <t>START_DATE</t>
-  </si>
-  <si>
-    <t>END_DATE</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,28 +371,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color rgb="FF002060"/>
       <name val="Arial"/>
@@ -454,7 +388,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,24 +433,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF974706"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE26B0A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -546,7 +462,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -843,21 +759,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF808080"/>
       </left>
       <right style="thin">
@@ -888,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -954,41 +855,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -998,40 +884,40 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1043,10 +929,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1054,9 +940,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1453,13 +1336,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="26.25" customHeight="1">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="9"/>
@@ -1483,95 +1366,95 @@
     </row>
     <row r="4" spans="2:6" ht="15"/>
     <row r="5" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="43" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="41" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="38" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B6" s="49"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="11"/>
-      <c r="F6" s="44"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B7" s="49"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="47"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B8" s="49"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="11"/>
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B9" s="49"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="47"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="40" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B10" s="49"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="47"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="11"/>
-      <c r="F10" s="44"/>
+      <c r="F10" s="39"/>
     </row>
     <row r="11" spans="2:6" ht="14.45" customHeight="1"/>
     <row r="14" spans="2:6" ht="16.5">
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="15">
-      <c r="C15" s="34"/>
-      <c r="D15" s="35" t="s">
+      <c r="C15" s="29"/>
+      <c r="D15" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15">
-      <c r="C16" s="36"/>
-      <c r="D16" s="35" t="s">
+      <c r="C16" s="31"/>
+      <c r="D16" s="30" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="15">
-      <c r="C17" s="37"/>
-      <c r="D17" s="35" t="s">
+      <c r="C17" s="32"/>
+      <c r="D17" s="30" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="15">
-      <c r="C18" s="38"/>
-      <c r="D18" s="35" t="s">
+      <c r="C18" s="33"/>
+      <c r="D18" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="15">
-      <c r="C19" s="39"/>
-      <c r="D19" s="35" t="s">
+      <c r="C19" s="34"/>
+      <c r="D19" s="30" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1650,36 +1533,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="54"/>
+      <c r="G2" s="49"/>
     </row>
     <row r="3" spans="1:7" ht="83.25" customHeight="1">
       <c r="A3" s="19">
@@ -1695,8 +1578,8 @@
         <v>31</v>
       </c>
       <c r="E3" s="22"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
     </row>
     <row r="4" spans="1:7" ht="45.75">
       <c r="A4" s="19">
@@ -1714,40 +1597,40 @@
       <c r="E4" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
     </row>
     <row r="6" spans="1:7" s="16" customFormat="1" ht="14.45" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="59"/>
+      <c r="G7" s="54"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="17">
@@ -1765,10 +1648,10 @@
       <c r="E8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="61"/>
+      <c r="G8" s="56"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1">
@@ -1786,10 +1669,10 @@
       <c r="E9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="57"/>
+      <c r="G9" s="52"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1">
@@ -1807,10 +1690,10 @@
       <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="52"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1">
@@ -1828,10 +1711,10 @@
       <c r="E11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="56" t="s">
+      <c r="F11" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="57"/>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1">
@@ -1849,10 +1732,10 @@
       <c r="E12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="56" t="s">
+      <c r="F12" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="57"/>
+      <c r="G12" s="52"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
@@ -1870,10 +1753,10 @@
       <c r="E13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="56" t="s">
+      <c r="F13" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="57"/>
+      <c r="G13" s="52"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
@@ -1891,10 +1774,10 @@
       <c r="E14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="56" t="s">
+      <c r="F14" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="57"/>
+      <c r="G14" s="52"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
@@ -1912,10 +1795,10 @@
       <c r="E15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="F15" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="57"/>
+      <c r="G15" s="52"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
@@ -1933,10 +1816,10 @@
       <c r="E16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="56" t="s">
+      <c r="F16" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="57"/>
+      <c r="G16" s="52"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1">
@@ -1954,10 +1837,10 @@
       <c r="E17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="56" t="s">
+      <c r="F17" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="57"/>
+      <c r="G17" s="52"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1">
@@ -1975,10 +1858,10 @@
       <c r="E18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="56" t="s">
+      <c r="F18" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="52"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1">
@@ -1996,10 +1879,10 @@
       <c r="E19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="56" t="s">
+      <c r="F19" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="57"/>
+      <c r="G19" s="52"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
@@ -2017,10 +1900,10 @@
       <c r="E20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="56" t="s">
+      <c r="F20" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="57"/>
+      <c r="G20" s="52"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
@@ -2038,10 +1921,10 @@
       <c r="E21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="57"/>
+      <c r="G21" s="52"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
@@ -2059,10 +1942,10 @@
       <c r="E22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="57"/>
+      <c r="G22" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -2089,444 +1972,6 @@
     <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319C8271-55E4-46CA-BA31-E01B95AC11BD}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="6" width="19.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210A4CF7-18D0-402A-8CB2-0F508A4C400C}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.85546875" style="27" customWidth="1"/>
-    <col min="2" max="5" width="17.85546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="27" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
